--- a/data_out/country_spreadsheets/Hungary.xlsx
+++ b/data_out/country_spreadsheets/Hungary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:AN21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>198.48</v>
       </c>
+      <c r="X2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>332.56</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>120.29</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>51.19</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>209.77</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>198.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>203.69</v>
       </c>
+      <c r="X3" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>311.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>77.56999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>244.4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>203.69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>194.72</v>
       </c>
+      <c r="X4" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>322.09</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>74.23</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>58.87</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>175.56</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>194.72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>142.4</v>
       </c>
+      <c r="X5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>336.08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>69.97</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>67.03</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>226.16</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>142.4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>154.25</v>
       </c>
+      <c r="X6" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>83.42</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>318.57</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>70.06999999999999</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>188.26</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>307.09</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>154.25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>91.68000000000001</v>
       </c>
+      <c r="X7" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>37.77</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>250.68</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>100.42</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>59.71</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>126.92</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>90.33</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>247.48</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>91.68000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>89.20999999999999</v>
       </c>
+      <c r="X8" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>182.06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>106.72</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>89.20999999999999</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>113.49</v>
       </c>
+      <c r="X9" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>309.29</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>70.56</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>136.58</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>167.55</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>113.49</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>175.95</v>
       </c>
+      <c r="X10" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>249.51</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>173.89</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>143.42</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>123.78</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>175.95</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>149.17</v>
       </c>
+      <c r="X11" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>69.01000000000001</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>284.89</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>65.61</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>83.95</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>62.59</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>169.56</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>170.07</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>149.17</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>192.92</v>
       </c>
+      <c r="X12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>73.34</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>292.81</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>48.78</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>188.24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>114.62</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>279.95</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>172.79</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>192.92</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>164.81</v>
       </c>
+      <c r="X13" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>77.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>262.55</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>81.09</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>121.35</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>222.41</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>43.81</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>164.81</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>120.46</v>
       </c>
+      <c r="X14" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>302.9</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>232.94</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>120.46</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>157.24</v>
       </c>
+      <c r="X15" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>279.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>64.81999999999999</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>232.9</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>30.64</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>157.24</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>250.41</v>
       </c>
+      <c r="X16" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>80.02</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>298.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>117.26</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>189</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>191.36</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>142.91</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>255.01</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>111.84</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>250.41</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>230.2</v>
       </c>
+      <c r="X17" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>83.83</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>315.38</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>79.63</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>65.41</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>138.68</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>329.54</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>56.19</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>230.2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>109.63</v>
       </c>
+      <c r="X18" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>116.02</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>272.98</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>133.44</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>172.34</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>112.13</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>198.96</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>78.79000000000001</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>196.97</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>109.63</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>190.94</v>
       </c>
+      <c r="X19" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>96.02</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>272.09</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>71.94</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>86.66</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>153.22</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>141.26</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>206.14</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>89.78</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>190.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>298.89</v>
       </c>
+      <c r="X20" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>77.81</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>317.76</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>138.13</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>158.47</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>160.98</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>309.19</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>135.18</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>298.89</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2082,6 +3136,57 @@
         <v>187.74</v>
       </c>
       <c r="W21" t="n">
+        <v>254.64</v>
+      </c>
+      <c r="X21" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>292.42</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>117.79</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>150.45</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>68.41</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>179.62</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>135.48</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>154.65</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>250.57</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>120.14</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>187.74</v>
+      </c>
+      <c r="AN21" t="n">
         <v>254.64</v>
       </c>
     </row>
